--- a/Tests/TestResults/Muskan_Binoy/ProgramOwner_TestDesign.xlsx
+++ b/Tests/TestResults/Muskan_Binoy/ProgramOwner_TestDesign.xlsx
@@ -810,7 +810,7 @@
     <row r="27" ht="42" customHeight="1" s="11">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>4. Test IDs of the form PO-0xx refer to the existing suite in ProgramOwnerControllerTests.cs; other names are methods in ProgramOwnerBoundaryDefectTests.cs or ProgramOwnerSeleniumFlowTests.cs.</t>
+          <t>4. Test IDs of the form PO-0xx refer to the existing suite in ProgramOwnerControllerTests.cs; other names are methods in ProgramOwnerBvaTests.cs, ProgramOwnerEctTests.cs, ProgramOwnerBasisPathTests.cs, ProgramOwnerDefectTests.cs or ProgramOwnerSeleniumFlowTests.cs.</t>
         </is>
       </c>
     </row>
